--- a/Deliverables/BOM/LCSC BOM For Quantity 5 Boards .xlsx
+++ b/Deliverables/BOM/LCSC BOM For Quantity 5 Boards .xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="275">
   <si>
     <t>Description</t>
   </si>
@@ -819,9 +819,6 @@
     <t xml:space="preserve">Jing </t>
   </si>
   <si>
-    <t xml:space="preserve">XINGLIGHT </t>
-  </si>
-  <si>
     <t>-------</t>
   </si>
   <si>
@@ -843,9 +840,6 @@
     <t>CC0603KRX7R6BB102</t>
   </si>
   <si>
-    <t>Alibaba</t>
-  </si>
-  <si>
     <t>Q5</t>
   </si>
   <si>
@@ -876,20 +870,16 @@
     <t>Total Cost(1)</t>
   </si>
   <si>
-    <t xml:space="preserve">XL-2835UWC-02
-</t>
-  </si>
-  <si>
     <t>IC DETECTOR VOLT 2.9V OD SSOP3</t>
   </si>
   <si>
     <t>BD48K29G-TL</t>
   </si>
   <si>
-    <t xml:space="preserve">urooj is part ki quoation chahiye alibaba an custom supplier se </t>
-  </si>
-  <si>
     <t>Chipmall</t>
+  </si>
+  <si>
+    <t>Custom supplier</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1016,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1045,12 +1035,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="29">
     <border>
@@ -1415,7 +1399,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1689,9 +1673,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1727,9 +1708,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1760,22 +1738,25 @@
     <xf numFmtId="165" fontId="14" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1787,14 +1768,14 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2092,7 +2073,7 @@
     <col min="10" max="11" width="19.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.42578125" style="6" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.140625" bestFit="1" customWidth="1"/>
@@ -2101,27 +2082,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="118" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="128"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="128"/>
-      <c r="O1" s="128"/>
-      <c r="P1" s="128"/>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="128"/>
-      <c r="S1" s="129"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="120"/>
     </row>
     <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -2152,10 +2133,10 @@
         <v>12</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>38</v>
@@ -2167,10 +2148,10 @@
         <v>37</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>206</v>
@@ -2205,7 +2186,7 @@
         <v>205</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>4</v>
@@ -2219,7 +2200,7 @@
       <c r="L3" s="20">
         <v>22</v>
       </c>
-      <c r="M3" s="103">
+      <c r="M3" s="102">
         <f>L3*5</f>
         <v>110</v>
       </c>
@@ -2236,7 +2217,7 @@
       <c r="Q3" s="5">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="R3" s="100">
+      <c r="R3" s="99">
         <f>Q3*K3</f>
         <v>0.64</v>
       </c>
@@ -2248,7 +2229,7 @@
       <c r="A4" s="12">
         <v>2</v>
       </c>
-      <c r="B4" s="123"/>
+      <c r="B4" s="121"/>
       <c r="C4" s="23" t="s">
         <v>81</v>
       </c>
@@ -2279,7 +2260,7 @@
       <c r="L4" s="27">
         <v>6</v>
       </c>
-      <c r="M4" s="105">
+      <c r="M4" s="104">
         <f t="shared" ref="M4:M52" si="0">L4*5</f>
         <v>30</v>
       </c>
@@ -2296,7 +2277,7 @@
       <c r="Q4" s="29">
         <v>0.25609999999999999</v>
       </c>
-      <c r="R4" s="102">
+      <c r="R4" s="101">
         <f t="shared" ref="R4:R52" si="2">Q4*K4</f>
         <v>8.9634999999999998</v>
       </c>
@@ -2304,11 +2285,11 @@
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
     </row>
-    <row r="5" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>3</v>
       </c>
-      <c r="B5" s="123"/>
+      <c r="B5" s="121"/>
       <c r="C5" s="23" t="s">
         <v>85</v>
       </c>
@@ -2339,26 +2320,28 @@
       <c r="L5" s="27">
         <v>3</v>
       </c>
-      <c r="M5" s="105">
+      <c r="M5" s="104">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="N5" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="O5" s="29"/>
+        <v>274</v>
+      </c>
+      <c r="O5" s="29">
+        <v>0.48</v>
+      </c>
       <c r="P5" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="102">
+        <v>2.4</v>
+      </c>
+      <c r="Q5" s="29">
+        <v>0.48</v>
+      </c>
+      <c r="R5" s="101">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S5" s="107" t="s">
-        <v>276</v>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="S5" s="126"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
     </row>
@@ -2366,7 +2349,7 @@
       <c r="A6" s="12">
         <v>4</v>
       </c>
-      <c r="B6" s="123"/>
+      <c r="B6" s="121"/>
       <c r="C6" s="23" t="s">
         <v>88</v>
       </c>
@@ -2397,7 +2380,7 @@
       <c r="L6" s="27">
         <v>1</v>
       </c>
-      <c r="M6" s="105">
+      <c r="M6" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -2414,7 +2397,7 @@
       <c r="Q6" s="29">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="R6" s="102">
+      <c r="R6" s="101">
         <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
@@ -2426,7 +2409,7 @@
       <c r="A7" s="12">
         <v>5</v>
       </c>
-      <c r="B7" s="123"/>
+      <c r="B7" s="121"/>
       <c r="C7" s="23" t="s">
         <v>90</v>
       </c>
@@ -2457,7 +2440,7 @@
       <c r="L7" s="27">
         <v>2</v>
       </c>
-      <c r="M7" s="105">
+      <c r="M7" s="104">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2474,7 +2457,7 @@
       <c r="Q7" s="29">
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="R7" s="102">
+      <c r="R7" s="101">
         <f t="shared" si="2"/>
         <v>0.48499999999999999</v>
       </c>
@@ -2486,7 +2469,7 @@
       <c r="A8" s="12">
         <v>6</v>
       </c>
-      <c r="B8" s="123"/>
+      <c r="B8" s="121"/>
       <c r="C8" s="23" t="s">
         <v>93</v>
       </c>
@@ -2503,7 +2486,7 @@
         <v>63</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I8" s="24" t="s">
         <v>75</v>
@@ -2517,7 +2500,7 @@
       <c r="L8" s="27">
         <v>1</v>
       </c>
-      <c r="M8" s="105">
+      <c r="M8" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -2534,7 +2517,7 @@
       <c r="Q8" s="29">
         <v>1.5E-3</v>
       </c>
-      <c r="R8" s="102">
+      <c r="R8" s="101">
         <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
@@ -2546,7 +2529,7 @@
       <c r="A9" s="12">
         <v>7</v>
       </c>
-      <c r="B9" s="123"/>
+      <c r="B9" s="121"/>
       <c r="C9" s="23" t="s">
         <v>97</v>
       </c>
@@ -2577,7 +2560,7 @@
       <c r="L9" s="27">
         <v>2</v>
       </c>
-      <c r="M9" s="105">
+      <c r="M9" s="104">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2594,7 +2577,7 @@
       <c r="Q9" s="29">
         <v>9.0300000000000005E-2</v>
       </c>
-      <c r="R9" s="102">
+      <c r="R9" s="101">
         <f t="shared" si="2"/>
         <v>1.3545</v>
       </c>
@@ -2606,7 +2589,7 @@
       <c r="A10" s="12">
         <v>8</v>
       </c>
-      <c r="B10" s="124"/>
+      <c r="B10" s="123"/>
       <c r="C10" s="32" t="s">
         <v>100</v>
       </c>
@@ -2623,7 +2606,7 @@
         <v>61</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I10" s="33" t="s">
         <v>76</v>
@@ -2637,7 +2620,7 @@
       <c r="L10" s="36">
         <v>1</v>
       </c>
-      <c r="M10" s="109">
+      <c r="M10" s="107">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -2654,7 +2637,7 @@
       <c r="Q10" s="38">
         <v>4.3E-3</v>
       </c>
-      <c r="R10" s="110">
+      <c r="R10" s="108">
         <f t="shared" si="2"/>
         <v>0.215</v>
       </c>
@@ -2666,10 +2649,10 @@
       <c r="A11" s="12">
         <v>9</v>
       </c>
-      <c r="B11" s="123" t="s">
+      <c r="B11" s="121" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="111" t="s">
+      <c r="C11" s="109" t="s">
         <v>241</v>
       </c>
       <c r="D11" s="39" t="s">
@@ -2684,22 +2667,22 @@
       <c r="G11" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="H11" s="112" t="s">
-        <v>210</v>
-      </c>
-      <c r="I11" s="112" t="s">
-        <v>210</v>
-      </c>
-      <c r="J11" s="112">
+      <c r="H11" s="110" t="s">
+        <v>210</v>
+      </c>
+      <c r="I11" s="110" t="s">
+        <v>210</v>
+      </c>
+      <c r="J11" s="110">
         <v>10</v>
       </c>
-      <c r="K11" s="112">
+      <c r="K11" s="110">
         <v>10</v>
       </c>
-      <c r="L11" s="113">
+      <c r="L11" s="111">
         <v>1</v>
       </c>
-      <c r="M11" s="114">
+      <c r="M11" s="112">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -2716,7 +2699,7 @@
       <c r="Q11" s="43">
         <v>7.5499999999999998E-2</v>
       </c>
-      <c r="R11" s="101">
+      <c r="R11" s="100">
         <f t="shared" si="2"/>
         <v>0.755</v>
       </c>
@@ -2728,7 +2711,7 @@
       <c r="A12" s="12">
         <v>10</v>
       </c>
-      <c r="B12" s="123"/>
+      <c r="B12" s="121"/>
       <c r="C12" s="23" t="s">
         <v>105</v>
       </c>
@@ -2759,7 +2742,7 @@
       <c r="L12" s="27">
         <v>1</v>
       </c>
-      <c r="M12" s="105">
+      <c r="M12" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -2776,7 +2759,7 @@
       <c r="Q12" s="29">
         <v>1.95E-2</v>
       </c>
-      <c r="R12" s="101">
+      <c r="R12" s="100">
         <f t="shared" si="2"/>
         <v>0.39</v>
       </c>
@@ -2788,7 +2771,7 @@
       <c r="A13" s="12">
         <v>11</v>
       </c>
-      <c r="B13" s="123"/>
+      <c r="B13" s="121"/>
       <c r="C13" s="46" t="s">
         <v>108</v>
       </c>
@@ -2816,10 +2799,10 @@
       <c r="K13" s="49">
         <v>15</v>
       </c>
-      <c r="L13" s="115">
+      <c r="L13" s="113">
         <v>2</v>
       </c>
-      <c r="M13" s="114">
+      <c r="M13" s="112">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2836,7 +2819,7 @@
       <c r="Q13" s="51">
         <v>0.1087</v>
       </c>
-      <c r="R13" s="116">
+      <c r="R13" s="114">
         <f t="shared" si="2"/>
         <v>1.6305000000000001</v>
       </c>
@@ -2881,7 +2864,7 @@
       <c r="L14" s="56">
         <v>1</v>
       </c>
-      <c r="M14" s="103">
+      <c r="M14" s="102">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -2906,11 +2889,11 @@
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
     </row>
-    <row r="15" spans="1:21" s="18" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" s="18" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12">
         <v>13</v>
       </c>
-      <c r="B15" s="123"/>
+      <c r="B15" s="121"/>
       <c r="C15" s="60" t="s">
         <v>213</v>
       </c>
@@ -2941,26 +2924,28 @@
       <c r="L15" s="92">
         <v>1</v>
       </c>
-      <c r="M15" s="105">
+      <c r="M15" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N15" s="93" t="s">
-        <v>262</v>
-      </c>
-      <c r="O15" s="29"/>
+      <c r="N15" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="O15" s="29">
+        <v>0.8</v>
+      </c>
       <c r="P15" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="94"/>
-      <c r="R15" s="101">
+        <v>1.6</v>
+      </c>
+      <c r="Q15" s="93">
+        <v>0.8</v>
+      </c>
+      <c r="R15" s="100">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="107" t="s">
-        <v>276</v>
-      </c>
+        <v>6.4</v>
+      </c>
+      <c r="S15" s="126"/>
       <c r="T15" s="17"/>
       <c r="U15" s="17"/>
     </row>
@@ -2968,7 +2953,7 @@
       <c r="A16" s="12">
         <v>14</v>
       </c>
-      <c r="B16" s="124"/>
+      <c r="B16" s="123"/>
       <c r="C16" s="61" t="s">
         <v>214</v>
       </c>
@@ -2999,7 +2984,7 @@
       <c r="L16" s="62">
         <v>1</v>
       </c>
-      <c r="M16" s="109">
+      <c r="M16" s="107">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3016,7 +3001,7 @@
       <c r="Q16" s="38">
         <v>7.0300000000000001E-2</v>
       </c>
-      <c r="R16" s="110">
+      <c r="R16" s="108">
         <f t="shared" si="2"/>
         <v>0.70300000000000007</v>
       </c>
@@ -3028,7 +3013,7 @@
       <c r="A17" s="12">
         <v>15</v>
       </c>
-      <c r="B17" s="123" t="s">
+      <c r="B17" s="121" t="s">
         <v>69</v>
       </c>
       <c r="C17" s="63" t="s">
@@ -3061,7 +3046,7 @@
       <c r="L17" s="64">
         <v>4</v>
       </c>
-      <c r="M17" s="104">
+      <c r="M17" s="103">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -3078,7 +3063,7 @@
       <c r="Q17" s="43">
         <v>1.52E-2</v>
       </c>
-      <c r="R17" s="101">
+      <c r="R17" s="100">
         <f t="shared" si="2"/>
         <v>0.76</v>
       </c>
@@ -3090,7 +3075,7 @@
       <c r="A18" s="12">
         <v>16</v>
       </c>
-      <c r="B18" s="123"/>
+      <c r="B18" s="121"/>
       <c r="C18" s="46" t="s">
         <v>119</v>
       </c>
@@ -3100,17 +3085,13 @@
       <c r="E18" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="F18" s="49" t="s">
-        <v>273</v>
-      </c>
-      <c r="G18" s="47" t="s">
+      <c r="F18" s="49"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="49" t="s">
+        <v>210</v>
+      </c>
+      <c r="I18" s="66" t="s">
         <v>254</v>
-      </c>
-      <c r="H18" s="49" t="s">
-        <v>210</v>
-      </c>
-      <c r="I18" s="66" t="s">
-        <v>255</v>
       </c>
       <c r="J18" s="66">
         <v>50</v>
@@ -3121,28 +3102,22 @@
       <c r="L18" s="67">
         <v>4</v>
       </c>
-      <c r="M18" s="103">
+      <c r="M18" s="102">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N18" s="50" t="s">
-        <v>239</v>
-      </c>
-      <c r="O18" s="51">
-        <v>8.6E-3</v>
-      </c>
+      <c r="N18" s="50"/>
+      <c r="O18" s="51"/>
       <c r="P18" s="51">
         <f t="shared" si="1"/>
-        <v>0.43</v>
-      </c>
-      <c r="Q18" s="51">
-        <v>8.6E-3</v>
-      </c>
-      <c r="R18" s="116">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="51"/>
+      <c r="R18" s="114">
         <f t="shared" si="2"/>
-        <v>0.43</v>
-      </c>
-      <c r="S18" s="117"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="115"/>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
     </row>
@@ -3168,10 +3143,10 @@
       <c r="G19" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="H19" s="106" t="s">
-        <v>210</v>
-      </c>
-      <c r="I19" s="106" t="s">
+      <c r="H19" s="105" t="s">
+        <v>210</v>
+      </c>
+      <c r="I19" s="105" t="s">
         <v>210</v>
       </c>
       <c r="J19" s="54">
@@ -3183,7 +3158,7 @@
       <c r="L19" s="69">
         <v>1</v>
       </c>
-      <c r="M19" s="103">
+      <c r="M19" s="102">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3212,12 +3187,12 @@
       <c r="A20" s="12">
         <v>18</v>
       </c>
-      <c r="B20" s="123"/>
+      <c r="B20" s="121"/>
       <c r="C20" s="23" t="s">
         <v>124</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E20" s="24" t="s">
         <v>57</v>
@@ -3243,7 +3218,7 @@
       <c r="L20" s="27">
         <v>1</v>
       </c>
-      <c r="M20" s="105">
+      <c r="M20" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3260,7 +3235,7 @@
       <c r="Q20" s="29">
         <v>6.1499999999999999E-2</v>
       </c>
-      <c r="R20" s="101">
+      <c r="R20" s="100">
         <f t="shared" si="2"/>
         <v>0.61499999999999999</v>
       </c>
@@ -3268,11 +3243,11 @@
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
     </row>
-    <row r="21" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12">
         <v>19</v>
       </c>
-      <c r="B21" s="124"/>
+      <c r="B21" s="123"/>
       <c r="C21" s="32" t="s">
         <v>125</v>
       </c>
@@ -3303,26 +3278,28 @@
       <c r="L21" s="36">
         <v>1</v>
       </c>
-      <c r="M21" s="109">
+      <c r="M21" s="107">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N21" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="O21" s="38"/>
+      <c r="N21" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="O21" s="38">
+        <v>0.63700000000000001</v>
+      </c>
       <c r="P21" s="38">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="110">
+        <v>1.274</v>
+      </c>
+      <c r="Q21" s="38">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="R21" s="108">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="118" t="s">
-        <v>276</v>
-      </c>
+        <v>5.0960000000000001</v>
+      </c>
+      <c r="S21" s="127"/>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
     </row>
@@ -3363,7 +3340,7 @@
       <c r="L22" s="69">
         <v>5</v>
       </c>
-      <c r="M22" s="103">
+      <c r="M22" s="102">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -3392,7 +3369,7 @@
       <c r="A23" s="12">
         <v>21</v>
       </c>
-      <c r="B23" s="123"/>
+      <c r="B23" s="121"/>
       <c r="C23" s="23" t="s">
         <v>132</v>
       </c>
@@ -3423,7 +3400,7 @@
       <c r="L23" s="27">
         <v>6</v>
       </c>
-      <c r="M23" s="105">
+      <c r="M23" s="104">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -3440,7 +3417,7 @@
       <c r="Q23" s="29">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="R23" s="101">
+      <c r="R23" s="100">
         <f t="shared" si="2"/>
         <v>0.11</v>
       </c>
@@ -3452,7 +3429,7 @@
       <c r="A24" s="12">
         <v>22</v>
       </c>
-      <c r="B24" s="123"/>
+      <c r="B24" s="121"/>
       <c r="C24" s="23" t="s">
         <v>135</v>
       </c>
@@ -3469,7 +3446,7 @@
         <v>218</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I24" s="24" t="s">
         <v>163</v>
@@ -3483,7 +3460,7 @@
       <c r="L24" s="27">
         <v>1</v>
       </c>
-      <c r="M24" s="105">
+      <c r="M24" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3500,7 +3477,7 @@
       <c r="Q24" s="29">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="R24" s="101">
+      <c r="R24" s="100">
         <f t="shared" si="2"/>
         <v>0.45999999999999996</v>
       </c>
@@ -3512,7 +3489,7 @@
       <c r="A25" s="12">
         <v>23</v>
       </c>
-      <c r="B25" s="123"/>
+      <c r="B25" s="121"/>
       <c r="C25" s="23" t="s">
         <v>137</v>
       </c>
@@ -3543,7 +3520,7 @@
       <c r="L25" s="27">
         <v>1</v>
       </c>
-      <c r="M25" s="105">
+      <c r="M25" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3560,7 +3537,7 @@
       <c r="Q25" s="29">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="R25" s="101">
+      <c r="R25" s="100">
         <f t="shared" si="2"/>
         <v>0.11</v>
       </c>
@@ -3572,7 +3549,7 @@
       <c r="A26" s="12">
         <v>24</v>
       </c>
-      <c r="B26" s="123"/>
+      <c r="B26" s="121"/>
       <c r="C26" s="23" t="s">
         <v>139</v>
       </c>
@@ -3603,7 +3580,7 @@
       <c r="L26" s="27">
         <v>7</v>
       </c>
-      <c r="M26" s="105">
+      <c r="M26" s="104">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -3620,7 +3597,7 @@
       <c r="Q26" s="29">
         <v>1.4E-3</v>
       </c>
-      <c r="R26" s="101">
+      <c r="R26" s="100">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
@@ -3632,7 +3609,7 @@
       <c r="A27" s="12">
         <v>25</v>
       </c>
-      <c r="B27" s="123"/>
+      <c r="B27" s="121"/>
       <c r="C27" s="23" t="s">
         <v>142</v>
       </c>
@@ -3663,7 +3640,7 @@
       <c r="L27" s="27">
         <v>1</v>
       </c>
-      <c r="M27" s="105">
+      <c r="M27" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3680,7 +3657,7 @@
       <c r="Q27" s="29">
         <v>0.1472</v>
       </c>
-      <c r="R27" s="101">
+      <c r="R27" s="100">
         <f t="shared" si="2"/>
         <v>1.472</v>
       </c>
@@ -3692,7 +3669,7 @@
       <c r="A28" s="12">
         <v>26</v>
       </c>
-      <c r="B28" s="123"/>
+      <c r="B28" s="121"/>
       <c r="C28" s="23" t="s">
         <v>146</v>
       </c>
@@ -3723,7 +3700,7 @@
       <c r="L28" s="27">
         <v>1</v>
       </c>
-      <c r="M28" s="105">
+      <c r="M28" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3740,7 +3717,7 @@
       <c r="Q28" s="29">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="R28" s="101">
+      <c r="R28" s="100">
         <f t="shared" si="2"/>
         <v>0.42</v>
       </c>
@@ -3752,7 +3729,7 @@
       <c r="A29" s="12">
         <v>27</v>
       </c>
-      <c r="B29" s="123"/>
+      <c r="B29" s="121"/>
       <c r="C29" s="60" t="s">
         <v>220</v>
       </c>
@@ -3783,7 +3760,7 @@
       <c r="L29" s="27">
         <v>1</v>
       </c>
-      <c r="M29" s="105">
+      <c r="M29" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3800,7 +3777,7 @@
       <c r="Q29" s="29">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="R29" s="101">
+      <c r="R29" s="100">
         <f t="shared" si="2"/>
         <v>0.26</v>
       </c>
@@ -3812,7 +3789,7 @@
       <c r="A30" s="12">
         <v>28</v>
       </c>
-      <c r="B30" s="123"/>
+      <c r="B30" s="121"/>
       <c r="C30" s="23" t="s">
         <v>149</v>
       </c>
@@ -3843,7 +3820,7 @@
       <c r="L30" s="27">
         <v>3</v>
       </c>
-      <c r="M30" s="105">
+      <c r="M30" s="104">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -3860,7 +3837,7 @@
       <c r="Q30" s="29">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R30" s="101">
+      <c r="R30" s="100">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
@@ -3872,7 +3849,7 @@
       <c r="A31" s="12">
         <v>29</v>
       </c>
-      <c r="B31" s="123"/>
+      <c r="B31" s="121"/>
       <c r="C31" s="23" t="s">
         <v>152</v>
       </c>
@@ -3903,7 +3880,7 @@
       <c r="L31" s="27">
         <v>1</v>
       </c>
-      <c r="M31" s="105">
+      <c r="M31" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3920,7 +3897,7 @@
       <c r="Q31" s="29">
         <v>1.5E-3</v>
       </c>
-      <c r="R31" s="101">
+      <c r="R31" s="100">
         <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
@@ -3928,31 +3905,31 @@
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
     </row>
-    <row r="32" spans="1:21" s="96" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" s="95" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12">
         <v>30</v>
       </c>
-      <c r="B32" s="123"/>
+      <c r="B32" s="121"/>
       <c r="C32" s="60" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E32" s="26" t="s">
         <v>130</v>
       </c>
       <c r="F32" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="G32" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="G32" s="25" t="s">
-        <v>268</v>
-      </c>
       <c r="H32" s="24" t="s">
         <v>210</v>
       </c>
       <c r="I32" s="26" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J32" s="26">
         <v>10</v>
@@ -3963,7 +3940,7 @@
       <c r="L32" s="86">
         <v>8</v>
       </c>
-      <c r="M32" s="105">
+      <c r="M32" s="104">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -3980,19 +3957,19 @@
       <c r="Q32" s="29">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="R32" s="101">
+      <c r="R32" s="100">
         <f t="shared" si="2"/>
         <v>1.7500000000000002</v>
       </c>
       <c r="S32" s="21"/>
-      <c r="T32" s="95"/>
-      <c r="U32" s="95"/>
+      <c r="T32" s="94"/>
+      <c r="U32" s="94"/>
     </row>
     <row r="33" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12">
         <v>31</v>
       </c>
-      <c r="B33" s="123"/>
+      <c r="B33" s="121"/>
       <c r="C33" s="60" t="s">
         <v>221</v>
       </c>
@@ -4023,7 +4000,7 @@
       <c r="L33" s="27">
         <v>1</v>
       </c>
-      <c r="M33" s="105">
+      <c r="M33" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -4040,7 +4017,7 @@
       <c r="Q33" s="29">
         <v>3.5700000000000003E-2</v>
       </c>
-      <c r="R33" s="101">
+      <c r="R33" s="100">
         <f t="shared" si="2"/>
         <v>0.35700000000000004</v>
       </c>
@@ -4052,7 +4029,7 @@
       <c r="A34" s="12">
         <v>32</v>
       </c>
-      <c r="B34" s="123"/>
+      <c r="B34" s="121"/>
       <c r="C34" s="23" t="s">
         <v>156</v>
       </c>
@@ -4083,7 +4060,7 @@
       <c r="L34" s="27">
         <v>1</v>
       </c>
-      <c r="M34" s="105">
+      <c r="M34" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -4100,7 +4077,7 @@
       <c r="Q34" s="29">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="R34" s="101">
+      <c r="R34" s="100">
         <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
@@ -4112,7 +4089,7 @@
       <c r="A35" s="12">
         <v>33</v>
       </c>
-      <c r="B35" s="124"/>
+      <c r="B35" s="123"/>
       <c r="C35" s="32" t="s">
         <v>159</v>
       </c>
@@ -4143,7 +4120,7 @@
       <c r="L35" s="36">
         <v>4</v>
       </c>
-      <c r="M35" s="109">
+      <c r="M35" s="107">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -4160,7 +4137,7 @@
       <c r="Q35" s="38">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="R35" s="110">
+      <c r="R35" s="108">
         <f t="shared" si="2"/>
         <v>1.98</v>
       </c>
@@ -4172,7 +4149,7 @@
       <c r="A36" s="12">
         <v>34</v>
       </c>
-      <c r="B36" s="123" t="s">
+      <c r="B36" s="121" t="s">
         <v>70</v>
       </c>
       <c r="C36" s="63" t="s">
@@ -4205,7 +4182,7 @@
       <c r="L36" s="41">
         <v>1</v>
       </c>
-      <c r="M36" s="104">
+      <c r="M36" s="103">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -4222,7 +4199,7 @@
       <c r="Q36" s="43">
         <v>5.1799999999999999E-2</v>
       </c>
-      <c r="R36" s="101">
+      <c r="R36" s="100">
         <f t="shared" si="2"/>
         <v>0.51800000000000002</v>
       </c>
@@ -4234,7 +4211,7 @@
       <c r="A37" s="12">
         <v>35</v>
       </c>
-      <c r="B37" s="123"/>
+      <c r="B37" s="121"/>
       <c r="C37" s="73" t="s">
         <v>222</v>
       </c>
@@ -4265,12 +4242,12 @@
       <c r="L37" s="74">
         <v>1</v>
       </c>
-      <c r="M37" s="103">
+      <c r="M37" s="102">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N37" s="50" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="O37" s="51">
         <v>0.105085</v>
@@ -4282,7 +4259,7 @@
       <c r="Q37" s="51">
         <v>9.8080000000000001E-2</v>
       </c>
-      <c r="R37" s="116">
+      <c r="R37" s="114">
         <f t="shared" si="2"/>
         <v>0.98080000000000001</v>
       </c>
@@ -4310,7 +4287,7 @@
         <v>60</v>
       </c>
       <c r="G38" s="55" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H38" s="54" t="s">
         <v>210</v>
@@ -4327,7 +4304,7 @@
       <c r="L38" s="69">
         <v>1</v>
       </c>
-      <c r="M38" s="103">
+      <c r="M38" s="102">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -4356,7 +4333,7 @@
       <c r="A39" s="12">
         <v>37</v>
       </c>
-      <c r="B39" s="123"/>
+      <c r="B39" s="121"/>
       <c r="C39" s="23" t="s">
         <v>176</v>
       </c>
@@ -4387,7 +4364,7 @@
       <c r="L39" s="27">
         <v>1</v>
       </c>
-      <c r="M39" s="105">
+      <c r="M39" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -4404,7 +4381,7 @@
       <c r="Q39" s="29">
         <v>0.37509999999999999</v>
       </c>
-      <c r="R39" s="101">
+      <c r="R39" s="100">
         <f t="shared" si="2"/>
         <v>2.2505999999999999</v>
       </c>
@@ -4412,13 +4389,13 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
     </row>
-    <row r="40" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12">
         <v>38</v>
       </c>
-      <c r="B40" s="123"/>
+      <c r="B40" s="121"/>
       <c r="C40" s="60" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D40" s="24" t="s">
         <v>33</v>
@@ -4427,7 +4404,7 @@
         <v>224</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G40" s="25" t="s">
         <v>225</v>
@@ -4447,34 +4424,36 @@
       <c r="L40" s="27">
         <v>1</v>
       </c>
-      <c r="M40" s="105">
+      <c r="M40" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N40" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="O40" s="29"/>
+        <v>274</v>
+      </c>
+      <c r="O40" s="29">
+        <v>1.115</v>
+      </c>
       <c r="P40" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="101">
+        <v>2.23</v>
+      </c>
+      <c r="Q40" s="29">
+        <v>1.115</v>
+      </c>
+      <c r="R40" s="100">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S40" s="107" t="s">
-        <v>276</v>
-      </c>
+        <v>6.6899999999999995</v>
+      </c>
+      <c r="S40" s="126"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
     </row>
-    <row r="41" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12">
         <v>39</v>
       </c>
-      <c r="B41" s="123"/>
+      <c r="B41" s="121"/>
       <c r="C41" s="23" t="s">
         <v>179</v>
       </c>
@@ -4505,34 +4484,36 @@
       <c r="L41" s="27">
         <v>1</v>
       </c>
-      <c r="M41" s="105">
+      <c r="M41" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N41" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="O41" s="29"/>
+        <v>274</v>
+      </c>
+      <c r="O41" s="29">
+        <v>2.0710000000000002</v>
+      </c>
       <c r="P41" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q41" s="29"/>
-      <c r="R41" s="101">
+        <v>4.1420000000000003</v>
+      </c>
+      <c r="Q41" s="29">
+        <v>2.0710000000000002</v>
+      </c>
+      <c r="R41" s="100">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S41" s="107" t="s">
-        <v>276</v>
-      </c>
+        <v>12.426000000000002</v>
+      </c>
+      <c r="S41" s="126"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
     </row>
-    <row r="42" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12">
         <v>40</v>
       </c>
-      <c r="B42" s="123"/>
+      <c r="B42" s="121"/>
       <c r="C42" s="60" t="s">
         <v>229</v>
       </c>
@@ -4563,34 +4544,36 @@
       <c r="L42" s="27">
         <v>1</v>
       </c>
-      <c r="M42" s="105">
+      <c r="M42" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N42" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="O42" s="29"/>
+        <v>274</v>
+      </c>
+      <c r="O42" s="29">
+        <v>0.47799999999999998</v>
+      </c>
       <c r="P42" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="101">
+        <v>0.95599999999999996</v>
+      </c>
+      <c r="Q42" s="29">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="R42" s="100">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S42" s="107" t="s">
-        <v>276</v>
-      </c>
+        <v>2.8679999999999999</v>
+      </c>
+      <c r="S42" s="126"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
     </row>
-    <row r="43" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12">
         <v>41</v>
       </c>
-      <c r="B43" s="123"/>
+      <c r="B43" s="121"/>
       <c r="C43" s="60" t="s">
         <v>67</v>
       </c>
@@ -4621,34 +4604,36 @@
       <c r="L43" s="27">
         <v>1</v>
       </c>
-      <c r="M43" s="105">
+      <c r="M43" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N43" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="O43" s="29"/>
+        <v>274</v>
+      </c>
+      <c r="O43" s="29">
+        <v>0.63700000000000001</v>
+      </c>
       <c r="P43" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="101">
+        <v>1.274</v>
+      </c>
+      <c r="Q43" s="29">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="R43" s="100">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="107" t="s">
-        <v>276</v>
-      </c>
+        <v>3.8220000000000001</v>
+      </c>
+      <c r="S43" s="126"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
     </row>
-    <row r="44" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12">
         <v>42</v>
       </c>
-      <c r="B44" s="123"/>
+      <c r="B44" s="121"/>
       <c r="C44" s="60" t="s">
         <v>232</v>
       </c>
@@ -4679,34 +4664,36 @@
       <c r="L44" s="27">
         <v>1</v>
       </c>
-      <c r="M44" s="105">
+      <c r="M44" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N44" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="O44" s="29"/>
+        <v>274</v>
+      </c>
+      <c r="O44" s="29">
+        <v>3.1850000000000001</v>
+      </c>
       <c r="P44" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q44" s="29"/>
-      <c r="R44" s="101">
+        <v>6.37</v>
+      </c>
+      <c r="Q44" s="29">
+        <v>3.1850000000000001</v>
+      </c>
+      <c r="R44" s="100">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S44" s="107" t="s">
-        <v>276</v>
-      </c>
+        <v>19.11</v>
+      </c>
+      <c r="S44" s="126"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
     </row>
-    <row r="45" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12">
         <v>43</v>
       </c>
-      <c r="B45" s="123"/>
+      <c r="B45" s="121"/>
       <c r="C45" s="60" t="s">
         <v>236</v>
       </c>
@@ -4737,34 +4724,36 @@
       <c r="L45" s="27">
         <v>1</v>
       </c>
-      <c r="M45" s="105">
+      <c r="M45" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N45" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="O45" s="29"/>
+        <v>274</v>
+      </c>
+      <c r="O45" s="29">
+        <v>3.1850000000000001</v>
+      </c>
       <c r="P45" s="29">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q45" s="29"/>
-      <c r="R45" s="101">
+        <v>6.37</v>
+      </c>
+      <c r="Q45" s="29">
+        <v>3.1850000000000001</v>
+      </c>
+      <c r="R45" s="100">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S45" s="107" t="s">
-        <v>276</v>
-      </c>
+        <v>19.11</v>
+      </c>
+      <c r="S45" s="126"/>
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
     </row>
-    <row r="46" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="12">
         <v>44</v>
       </c>
-      <c r="B46" s="124"/>
+      <c r="B46" s="123"/>
       <c r="C46" s="32" t="s">
         <v>184</v>
       </c>
@@ -4795,26 +4784,28 @@
       <c r="L46" s="36">
         <v>1</v>
       </c>
-      <c r="M46" s="109">
+      <c r="M46" s="107">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N46" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="O46" s="38"/>
+      <c r="N46" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="O46" s="38">
+        <v>0.95599999999999996</v>
+      </c>
       <c r="P46" s="38">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q46" s="38"/>
-      <c r="R46" s="110">
+        <v>1.9119999999999999</v>
+      </c>
+      <c r="Q46" s="38">
+        <v>0.95599999999999996</v>
+      </c>
+      <c r="R46" s="108">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S46" s="118" t="s">
-        <v>276</v>
-      </c>
+        <v>5.7359999999999998</v>
+      </c>
+      <c r="S46" s="127"/>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
     </row>
@@ -4822,7 +4813,7 @@
       <c r="A47" s="12">
         <v>45</v>
       </c>
-      <c r="B47" s="97" t="s">
+      <c r="B47" s="96" t="s">
         <v>237</v>
       </c>
       <c r="C47" s="76" t="s">
@@ -4855,7 +4846,7 @@
       <c r="L47" s="78">
         <v>1</v>
       </c>
-      <c r="M47" s="114">
+      <c r="M47" s="112">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -4872,7 +4863,7 @@
       <c r="Q47" s="80">
         <v>0.28570000000000001</v>
       </c>
-      <c r="R47" s="116">
+      <c r="R47" s="114">
         <f t="shared" si="2"/>
         <v>1.7141999999999999</v>
       </c>
@@ -4880,7 +4871,7 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
     </row>
-    <row r="48" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12">
         <v>46</v>
       </c>
@@ -4903,17 +4894,17 @@
         <v>247</v>
       </c>
       <c r="H48" s="55" t="s">
+        <v>256</v>
+      </c>
+      <c r="I48" s="55" t="s">
         <v>257</v>
-      </c>
-      <c r="I48" s="55" t="s">
-        <v>258</v>
       </c>
       <c r="J48" s="55"/>
       <c r="K48" s="55"/>
       <c r="L48" s="56">
         <v>1</v>
       </c>
-      <c r="M48" s="103">
+      <c r="M48" s="102">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -4928,9 +4919,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S48" s="119" t="s">
-        <v>276</v>
-      </c>
+      <c r="S48" s="128"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
     </row>
@@ -4938,7 +4927,7 @@
       <c r="A49" s="12">
         <v>47</v>
       </c>
-      <c r="B49" s="123"/>
+      <c r="B49" s="121"/>
       <c r="C49" s="23" t="s">
         <v>191</v>
       </c>
@@ -4969,7 +4958,7 @@
       <c r="L49" s="84">
         <v>2</v>
       </c>
-      <c r="M49" s="105">
+      <c r="M49" s="104">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -4986,7 +4975,7 @@
       <c r="Q49" s="29">
         <v>4.4699999999999997E-2</v>
       </c>
-      <c r="R49" s="101">
+      <c r="R49" s="100">
         <f t="shared" si="2"/>
         <v>0.44699999999999995</v>
       </c>
@@ -4998,7 +4987,7 @@
       <c r="A50" s="12">
         <v>48</v>
       </c>
-      <c r="B50" s="123"/>
+      <c r="B50" s="121"/>
       <c r="C50" s="23" t="s">
         <v>194</v>
       </c>
@@ -5029,7 +5018,7 @@
       <c r="L50" s="86">
         <v>1</v>
       </c>
-      <c r="M50" s="105">
+      <c r="M50" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -5046,7 +5035,7 @@
       <c r="Q50" s="29">
         <v>0.11650000000000001</v>
       </c>
-      <c r="R50" s="101">
+      <c r="R50" s="100">
         <f t="shared" si="2"/>
         <v>1.165</v>
       </c>
@@ -5058,7 +5047,7 @@
       <c r="A51" s="12">
         <v>49</v>
       </c>
-      <c r="B51" s="123"/>
+      <c r="B51" s="121"/>
       <c r="C51" s="23" t="s">
         <v>197</v>
       </c>
@@ -5089,7 +5078,7 @@
       <c r="L51" s="86">
         <v>1</v>
       </c>
-      <c r="M51" s="105">
+      <c r="M51" s="104">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -5106,7 +5095,7 @@
       <c r="Q51" s="29">
         <v>5.4899999999999997E-2</v>
       </c>
-      <c r="R51" s="101">
+      <c r="R51" s="100">
         <f t="shared" si="2"/>
         <v>0.54899999999999993</v>
       </c>
@@ -5115,10 +5104,10 @@
       <c r="U51" s="3"/>
     </row>
     <row r="52" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="108">
+      <c r="A52" s="106">
         <v>50</v>
       </c>
-      <c r="B52" s="124"/>
+      <c r="B52" s="123"/>
       <c r="C52" s="32" t="s">
         <v>201</v>
       </c>
@@ -5149,7 +5138,7 @@
       <c r="L52" s="88">
         <v>1</v>
       </c>
-      <c r="M52" s="109">
+      <c r="M52" s="107">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -5166,7 +5155,7 @@
       <c r="Q52" s="38">
         <v>0.1085</v>
       </c>
-      <c r="R52" s="110">
+      <c r="R52" s="108">
         <f t="shared" si="2"/>
         <v>1.085</v>
       </c>
@@ -5175,32 +5164,32 @@
       <c r="U52" s="3"/>
     </row>
     <row r="53" spans="1:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M53" s="125" t="s">
+      <c r="M53" s="124" t="s">
         <v>17</v>
       </c>
-      <c r="N53" s="125"/>
-      <c r="O53" s="98"/>
-      <c r="P53" s="120">
+      <c r="N53" s="124"/>
+      <c r="O53" s="97"/>
+      <c r="P53" s="116">
         <f>SUM(P3:P52)</f>
-        <v>31.280069999999995</v>
+        <v>59.378070000000001</v>
       </c>
       <c r="R53" s="13">
         <f>SUM(R3:R52)</f>
-        <v>74.912500000000009</v>
+        <v>165.34049999999999</v>
       </c>
       <c r="T53" s="3"/>
       <c r="U53" s="3"/>
     </row>
     <row r="54" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M54" s="126" t="s">
+      <c r="M54" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="N54" s="126"/>
-      <c r="O54" s="99"/>
-      <c r="P54" s="99"/>
-      <c r="R54" s="121">
+      <c r="N54" s="125"/>
+      <c r="O54" s="98"/>
+      <c r="P54" s="98"/>
+      <c r="R54" s="117">
         <f>R53/5</f>
-        <v>14.982500000000002</v>
+        <v>33.068100000000001</v>
       </c>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
@@ -5239,11 +5228,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B3:B10"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B17:B18"/>
     <mergeCell ref="B48:B52"/>
     <mergeCell ref="M53:N53"/>
     <mergeCell ref="M54:N54"/>
@@ -5251,6 +5235,11 @@
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="B38:B46"/>
     <mergeCell ref="B22:B35"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B3:B10"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B18"/>
   </mergeCells>
   <conditionalFormatting sqref="S19:S20">
     <cfRule type="dataBar" priority="23">
@@ -5345,46 +5334,35 @@
     <hyperlink ref="N47" r:id="rId10"/>
     <hyperlink ref="N49" r:id="rId11"/>
     <hyperlink ref="N50" r:id="rId12"/>
-    <hyperlink ref="N18" r:id="rId13"/>
-    <hyperlink ref="N44" r:id="rId14"/>
-    <hyperlink ref="N9" r:id="rId15"/>
-    <hyperlink ref="N3" r:id="rId16"/>
-    <hyperlink ref="N6" r:id="rId17"/>
-    <hyperlink ref="N7" r:id="rId18"/>
-    <hyperlink ref="N13" r:id="rId19"/>
-    <hyperlink ref="N16" r:id="rId20"/>
-    <hyperlink ref="N22" r:id="rId21"/>
-    <hyperlink ref="N23" r:id="rId22"/>
-    <hyperlink ref="N26" r:id="rId23"/>
-    <hyperlink ref="N28" r:id="rId24"/>
-    <hyperlink ref="N29" r:id="rId25"/>
-    <hyperlink ref="N30" r:id="rId26"/>
-    <hyperlink ref="N31" r:id="rId27"/>
-    <hyperlink ref="N33" r:id="rId28"/>
-    <hyperlink ref="N34" r:id="rId29"/>
-    <hyperlink ref="N35" r:id="rId30"/>
-    <hyperlink ref="N24" r:id="rId31"/>
-    <hyperlink ref="N8" r:id="rId32"/>
-    <hyperlink ref="N10" r:id="rId33"/>
-    <hyperlink ref="N32" r:id="rId34"/>
-    <hyperlink ref="N51" r:id="rId35"/>
-    <hyperlink ref="N4" r:id="rId36"/>
-    <hyperlink ref="N19" r:id="rId37"/>
-    <hyperlink ref="N38" r:id="rId38"/>
-    <hyperlink ref="N52" r:id="rId39"/>
-    <hyperlink ref="N5" r:id="rId40"/>
-    <hyperlink ref="N15" r:id="rId41"/>
-    <hyperlink ref="N21" r:id="rId42"/>
-    <hyperlink ref="N37" r:id="rId43"/>
-    <hyperlink ref="N40" r:id="rId44"/>
-    <hyperlink ref="N41" r:id="rId45"/>
-    <hyperlink ref="N42" r:id="rId46"/>
-    <hyperlink ref="N43" r:id="rId47"/>
-    <hyperlink ref="N45" r:id="rId48"/>
-    <hyperlink ref="N46" r:id="rId49"/>
+    <hyperlink ref="N9" r:id="rId13"/>
+    <hyperlink ref="N3" r:id="rId14"/>
+    <hyperlink ref="N6" r:id="rId15"/>
+    <hyperlink ref="N7" r:id="rId16"/>
+    <hyperlink ref="N13" r:id="rId17"/>
+    <hyperlink ref="N16" r:id="rId18"/>
+    <hyperlink ref="N22" r:id="rId19"/>
+    <hyperlink ref="N23" r:id="rId20"/>
+    <hyperlink ref="N26" r:id="rId21"/>
+    <hyperlink ref="N28" r:id="rId22"/>
+    <hyperlink ref="N29" r:id="rId23"/>
+    <hyperlink ref="N30" r:id="rId24"/>
+    <hyperlink ref="N31" r:id="rId25"/>
+    <hyperlink ref="N33" r:id="rId26"/>
+    <hyperlink ref="N34" r:id="rId27"/>
+    <hyperlink ref="N35" r:id="rId28"/>
+    <hyperlink ref="N24" r:id="rId29"/>
+    <hyperlink ref="N8" r:id="rId30"/>
+    <hyperlink ref="N10" r:id="rId31"/>
+    <hyperlink ref="N32" r:id="rId32"/>
+    <hyperlink ref="N51" r:id="rId33"/>
+    <hyperlink ref="N4" r:id="rId34"/>
+    <hyperlink ref="N19" r:id="rId35"/>
+    <hyperlink ref="N38" r:id="rId36"/>
+    <hyperlink ref="N52" r:id="rId37"/>
+    <hyperlink ref="N37" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId50"/>
+  <pageSetup orientation="portrait" r:id="rId39"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/Deliverables/BOM/LCSC BOM For Quantity 5 Boards .xlsx
+++ b/Deliverables/BOM/LCSC BOM For Quantity 5 Boards .xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Github\BriacBarthes-PhoneCharger\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\BriacBarthes-PhoneCharger\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CFF2A8-17F7-427E-8D5D-1559AF8C25A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="14010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Briac" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +25,6 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -885,7 +885,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
@@ -1744,19 +1744,19 @@
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1768,14 +1768,14 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2057,7 +2057,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2082,27 +2082,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="126" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="120"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="128"/>
     </row>
     <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -2167,7 +2167,7 @@
       <c r="A3" s="12">
         <v>1</v>
       </c>
-      <c r="B3" s="122" t="s">
+      <c r="B3" s="121" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="19" t="s">
@@ -2229,7 +2229,7 @@
       <c r="A4" s="12">
         <v>2</v>
       </c>
-      <c r="B4" s="121"/>
+      <c r="B4" s="122"/>
       <c r="C4" s="23" t="s">
         <v>81</v>
       </c>
@@ -2289,7 +2289,7 @@
       <c r="A5" s="12">
         <v>3</v>
       </c>
-      <c r="B5" s="121"/>
+      <c r="B5" s="122"/>
       <c r="C5" s="23" t="s">
         <v>85</v>
       </c>
@@ -2341,7 +2341,7 @@
         <f t="shared" si="2"/>
         <v>9.6</v>
       </c>
-      <c r="S5" s="126"/>
+      <c r="S5" s="118"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
     </row>
@@ -2349,7 +2349,7 @@
       <c r="A6" s="12">
         <v>4</v>
       </c>
-      <c r="B6" s="121"/>
+      <c r="B6" s="122"/>
       <c r="C6" s="23" t="s">
         <v>88</v>
       </c>
@@ -2409,7 +2409,7 @@
       <c r="A7" s="12">
         <v>5</v>
       </c>
-      <c r="B7" s="121"/>
+      <c r="B7" s="122"/>
       <c r="C7" s="23" t="s">
         <v>90</v>
       </c>
@@ -2469,7 +2469,7 @@
       <c r="A8" s="12">
         <v>6</v>
       </c>
-      <c r="B8" s="121"/>
+      <c r="B8" s="122"/>
       <c r="C8" s="23" t="s">
         <v>93</v>
       </c>
@@ -2529,7 +2529,7 @@
       <c r="A9" s="12">
         <v>7</v>
       </c>
-      <c r="B9" s="121"/>
+      <c r="B9" s="122"/>
       <c r="C9" s="23" t="s">
         <v>97</v>
       </c>
@@ -2649,7 +2649,7 @@
       <c r="A11" s="12">
         <v>9</v>
       </c>
-      <c r="B11" s="121" t="s">
+      <c r="B11" s="122" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="109" t="s">
@@ -2711,7 +2711,7 @@
       <c r="A12" s="12">
         <v>10</v>
       </c>
-      <c r="B12" s="121"/>
+      <c r="B12" s="122"/>
       <c r="C12" s="23" t="s">
         <v>105</v>
       </c>
@@ -2771,7 +2771,7 @@
       <c r="A13" s="12">
         <v>11</v>
       </c>
-      <c r="B13" s="121"/>
+      <c r="B13" s="122"/>
       <c r="C13" s="46" t="s">
         <v>108</v>
       </c>
@@ -2831,7 +2831,7 @@
       <c r="A14" s="12">
         <v>12</v>
       </c>
-      <c r="B14" s="122" t="s">
+      <c r="B14" s="121" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="53" t="s">
@@ -2893,7 +2893,7 @@
       <c r="A15" s="12">
         <v>13</v>
       </c>
-      <c r="B15" s="121"/>
+      <c r="B15" s="122"/>
       <c r="C15" s="60" t="s">
         <v>213</v>
       </c>
@@ -2945,7 +2945,7 @@
         <f t="shared" si="2"/>
         <v>6.4</v>
       </c>
-      <c r="S15" s="126"/>
+      <c r="S15" s="118"/>
       <c r="T15" s="17"/>
       <c r="U15" s="17"/>
     </row>
@@ -3013,7 +3013,7 @@
       <c r="A17" s="12">
         <v>15</v>
       </c>
-      <c r="B17" s="121" t="s">
+      <c r="B17" s="122" t="s">
         <v>69</v>
       </c>
       <c r="C17" s="63" t="s">
@@ -3075,7 +3075,7 @@
       <c r="A18" s="12">
         <v>16</v>
       </c>
-      <c r="B18" s="121"/>
+      <c r="B18" s="122"/>
       <c r="C18" s="46" t="s">
         <v>119</v>
       </c>
@@ -3125,7 +3125,7 @@
       <c r="A19" s="12">
         <v>17</v>
       </c>
-      <c r="B19" s="122" t="s">
+      <c r="B19" s="121" t="s">
         <v>26</v>
       </c>
       <c r="C19" s="53" t="s">
@@ -3187,7 +3187,7 @@
       <c r="A20" s="12">
         <v>18</v>
       </c>
-      <c r="B20" s="121"/>
+      <c r="B20" s="122"/>
       <c r="C20" s="23" t="s">
         <v>124</v>
       </c>
@@ -3299,7 +3299,7 @@
         <f t="shared" si="2"/>
         <v>5.0960000000000001</v>
       </c>
-      <c r="S21" s="127"/>
+      <c r="S21" s="119"/>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
     </row>
@@ -3307,7 +3307,7 @@
       <c r="A22" s="12">
         <v>20</v>
       </c>
-      <c r="B22" s="122" t="s">
+      <c r="B22" s="121" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="53" t="s">
@@ -3369,7 +3369,7 @@
       <c r="A23" s="12">
         <v>21</v>
       </c>
-      <c r="B23" s="121"/>
+      <c r="B23" s="122"/>
       <c r="C23" s="23" t="s">
         <v>132</v>
       </c>
@@ -3429,7 +3429,7 @@
       <c r="A24" s="12">
         <v>22</v>
       </c>
-      <c r="B24" s="121"/>
+      <c r="B24" s="122"/>
       <c r="C24" s="23" t="s">
         <v>135</v>
       </c>
@@ -3489,7 +3489,7 @@
       <c r="A25" s="12">
         <v>23</v>
       </c>
-      <c r="B25" s="121"/>
+      <c r="B25" s="122"/>
       <c r="C25" s="23" t="s">
         <v>137</v>
       </c>
@@ -3549,7 +3549,7 @@
       <c r="A26" s="12">
         <v>24</v>
       </c>
-      <c r="B26" s="121"/>
+      <c r="B26" s="122"/>
       <c r="C26" s="23" t="s">
         <v>139</v>
       </c>
@@ -3609,7 +3609,7 @@
       <c r="A27" s="12">
         <v>25</v>
       </c>
-      <c r="B27" s="121"/>
+      <c r="B27" s="122"/>
       <c r="C27" s="23" t="s">
         <v>142</v>
       </c>
@@ -3669,7 +3669,7 @@
       <c r="A28" s="12">
         <v>26</v>
       </c>
-      <c r="B28" s="121"/>
+      <c r="B28" s="122"/>
       <c r="C28" s="23" t="s">
         <v>146</v>
       </c>
@@ -3729,7 +3729,7 @@
       <c r="A29" s="12">
         <v>27</v>
       </c>
-      <c r="B29" s="121"/>
+      <c r="B29" s="122"/>
       <c r="C29" s="60" t="s">
         <v>220</v>
       </c>
@@ -3789,7 +3789,7 @@
       <c r="A30" s="12">
         <v>28</v>
       </c>
-      <c r="B30" s="121"/>
+      <c r="B30" s="122"/>
       <c r="C30" s="23" t="s">
         <v>149</v>
       </c>
@@ -3849,7 +3849,7 @@
       <c r="A31" s="12">
         <v>29</v>
       </c>
-      <c r="B31" s="121"/>
+      <c r="B31" s="122"/>
       <c r="C31" s="23" t="s">
         <v>152</v>
       </c>
@@ -3909,7 +3909,7 @@
       <c r="A32" s="12">
         <v>30</v>
       </c>
-      <c r="B32" s="121"/>
+      <c r="B32" s="122"/>
       <c r="C32" s="60" t="s">
         <v>262</v>
       </c>
@@ -3969,7 +3969,7 @@
       <c r="A33" s="12">
         <v>31</v>
       </c>
-      <c r="B33" s="121"/>
+      <c r="B33" s="122"/>
       <c r="C33" s="60" t="s">
         <v>221</v>
       </c>
@@ -4029,7 +4029,7 @@
       <c r="A34" s="12">
         <v>32</v>
       </c>
-      <c r="B34" s="121"/>
+      <c r="B34" s="122"/>
       <c r="C34" s="23" t="s">
         <v>156</v>
       </c>
@@ -4149,7 +4149,7 @@
       <c r="A36" s="12">
         <v>34</v>
       </c>
-      <c r="B36" s="121" t="s">
+      <c r="B36" s="122" t="s">
         <v>70</v>
       </c>
       <c r="C36" s="63" t="s">
@@ -4211,7 +4211,7 @@
       <c r="A37" s="12">
         <v>35</v>
       </c>
-      <c r="B37" s="121"/>
+      <c r="B37" s="122"/>
       <c r="C37" s="73" t="s">
         <v>222</v>
       </c>
@@ -4271,7 +4271,7 @@
       <c r="A38" s="12">
         <v>36</v>
       </c>
-      <c r="B38" s="122" t="s">
+      <c r="B38" s="121" t="s">
         <v>71</v>
       </c>
       <c r="C38" s="53" t="s">
@@ -4333,7 +4333,7 @@
       <c r="A39" s="12">
         <v>37</v>
       </c>
-      <c r="B39" s="121"/>
+      <c r="B39" s="122"/>
       <c r="C39" s="23" t="s">
         <v>176</v>
       </c>
@@ -4393,7 +4393,7 @@
       <c r="A40" s="12">
         <v>38</v>
       </c>
-      <c r="B40" s="121"/>
+      <c r="B40" s="122"/>
       <c r="C40" s="60" t="s">
         <v>271</v>
       </c>
@@ -4445,7 +4445,7 @@
         <f t="shared" si="2"/>
         <v>6.6899999999999995</v>
       </c>
-      <c r="S40" s="126"/>
+      <c r="S40" s="118"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
     </row>
@@ -4453,7 +4453,7 @@
       <c r="A41" s="12">
         <v>39</v>
       </c>
-      <c r="B41" s="121"/>
+      <c r="B41" s="122"/>
       <c r="C41" s="23" t="s">
         <v>179</v>
       </c>
@@ -4505,7 +4505,7 @@
         <f t="shared" si="2"/>
         <v>12.426000000000002</v>
       </c>
-      <c r="S41" s="126"/>
+      <c r="S41" s="118"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
     </row>
@@ -4513,7 +4513,7 @@
       <c r="A42" s="12">
         <v>40</v>
       </c>
-      <c r="B42" s="121"/>
+      <c r="B42" s="122"/>
       <c r="C42" s="60" t="s">
         <v>229</v>
       </c>
@@ -4565,7 +4565,7 @@
         <f t="shared" si="2"/>
         <v>2.8679999999999999</v>
       </c>
-      <c r="S42" s="126"/>
+      <c r="S42" s="118"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
     </row>
@@ -4573,7 +4573,7 @@
       <c r="A43" s="12">
         <v>41</v>
       </c>
-      <c r="B43" s="121"/>
+      <c r="B43" s="122"/>
       <c r="C43" s="60" t="s">
         <v>67</v>
       </c>
@@ -4625,7 +4625,7 @@
         <f t="shared" si="2"/>
         <v>3.8220000000000001</v>
       </c>
-      <c r="S43" s="126"/>
+      <c r="S43" s="118"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
     </row>
@@ -4633,7 +4633,7 @@
       <c r="A44" s="12">
         <v>42</v>
       </c>
-      <c r="B44" s="121"/>
+      <c r="B44" s="122"/>
       <c r="C44" s="60" t="s">
         <v>232</v>
       </c>
@@ -4685,7 +4685,7 @@
         <f t="shared" si="2"/>
         <v>19.11</v>
       </c>
-      <c r="S44" s="126"/>
+      <c r="S44" s="118"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
     </row>
@@ -4693,7 +4693,7 @@
       <c r="A45" s="12">
         <v>43</v>
       </c>
-      <c r="B45" s="121"/>
+      <c r="B45" s="122"/>
       <c r="C45" s="60" t="s">
         <v>236</v>
       </c>
@@ -4745,7 +4745,7 @@
         <f t="shared" si="2"/>
         <v>19.11</v>
       </c>
-      <c r="S45" s="126"/>
+      <c r="S45" s="118"/>
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
     </row>
@@ -4805,7 +4805,7 @@
         <f t="shared" si="2"/>
         <v>5.7359999999999998</v>
       </c>
-      <c r="S46" s="127"/>
+      <c r="S46" s="119"/>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
     </row>
@@ -4875,7 +4875,7 @@
       <c r="A48" s="12">
         <v>46</v>
       </c>
-      <c r="B48" s="122" t="s">
+      <c r="B48" s="121" t="s">
         <v>72</v>
       </c>
       <c r="C48" s="53" t="s">
@@ -4919,7 +4919,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S48" s="128"/>
+      <c r="S48" s="120"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
     </row>
@@ -4927,7 +4927,7 @@
       <c r="A49" s="12">
         <v>47</v>
       </c>
-      <c r="B49" s="121"/>
+      <c r="B49" s="122"/>
       <c r="C49" s="23" t="s">
         <v>191</v>
       </c>
@@ -4987,7 +4987,7 @@
       <c r="A50" s="12">
         <v>48</v>
       </c>
-      <c r="B50" s="121"/>
+      <c r="B50" s="122"/>
       <c r="C50" s="23" t="s">
         <v>194</v>
       </c>
@@ -5047,7 +5047,7 @@
       <c r="A51" s="12">
         <v>49</v>
       </c>
-      <c r="B51" s="121"/>
+      <c r="B51" s="122"/>
       <c r="C51" s="23" t="s">
         <v>197</v>
       </c>
@@ -5228,6 +5228,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B3:B10"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B18"/>
     <mergeCell ref="B48:B52"/>
     <mergeCell ref="M53:N53"/>
     <mergeCell ref="M54:N54"/>
@@ -5235,11 +5240,6 @@
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="B38:B46"/>
     <mergeCell ref="B22:B35"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B3:B10"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B17:B18"/>
   </mergeCells>
   <conditionalFormatting sqref="S19:S20">
     <cfRule type="dataBar" priority="23">
@@ -5322,44 +5322,44 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N11" r:id="rId1"/>
-    <hyperlink ref="N12" r:id="rId2"/>
-    <hyperlink ref="N14" r:id="rId3"/>
-    <hyperlink ref="N17" r:id="rId4"/>
-    <hyperlink ref="N20" r:id="rId5"/>
-    <hyperlink ref="N25" r:id="rId6"/>
-    <hyperlink ref="N27" r:id="rId7"/>
-    <hyperlink ref="N36" r:id="rId8"/>
-    <hyperlink ref="N39" r:id="rId9"/>
-    <hyperlink ref="N47" r:id="rId10"/>
-    <hyperlink ref="N49" r:id="rId11"/>
-    <hyperlink ref="N50" r:id="rId12"/>
-    <hyperlink ref="N9" r:id="rId13"/>
-    <hyperlink ref="N3" r:id="rId14"/>
-    <hyperlink ref="N6" r:id="rId15"/>
-    <hyperlink ref="N7" r:id="rId16"/>
-    <hyperlink ref="N13" r:id="rId17"/>
-    <hyperlink ref="N16" r:id="rId18"/>
-    <hyperlink ref="N22" r:id="rId19"/>
-    <hyperlink ref="N23" r:id="rId20"/>
-    <hyperlink ref="N26" r:id="rId21"/>
-    <hyperlink ref="N28" r:id="rId22"/>
-    <hyperlink ref="N29" r:id="rId23"/>
-    <hyperlink ref="N30" r:id="rId24"/>
-    <hyperlink ref="N31" r:id="rId25"/>
-    <hyperlink ref="N33" r:id="rId26"/>
-    <hyperlink ref="N34" r:id="rId27"/>
-    <hyperlink ref="N35" r:id="rId28"/>
-    <hyperlink ref="N24" r:id="rId29"/>
-    <hyperlink ref="N8" r:id="rId30"/>
-    <hyperlink ref="N10" r:id="rId31"/>
-    <hyperlink ref="N32" r:id="rId32"/>
-    <hyperlink ref="N51" r:id="rId33"/>
-    <hyperlink ref="N4" r:id="rId34"/>
-    <hyperlink ref="N19" r:id="rId35"/>
-    <hyperlink ref="N38" r:id="rId36"/>
-    <hyperlink ref="N52" r:id="rId37"/>
-    <hyperlink ref="N37" r:id="rId38"/>
+    <hyperlink ref="N11" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N14" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N17" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N20" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N25" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N27" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N36" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N39" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N47" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N49" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N50" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N9" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N3" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N6" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N7" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N13" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N16" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N22" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N23" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N26" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N28" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N29" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N30" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N31" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N33" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N34" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N35" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N24" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N8" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N10" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="N32" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N51" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N4" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N19" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="N38" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="N52" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId39"/>
